--- a/stage_3.xlsx
+++ b/stage_3.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,6 +458,4526 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1360000077</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>@EEE_IE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>حسن مازن مكي</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>جمعيات اسكان الموانئ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-05-13 20:10:24.155</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6382645701</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>@abbas_xyz</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>عباس عبدالباقي جاسم</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>الحكيمية</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-05-13 20:13:39.848</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>321173824</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>@M_7MD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>محمد ستار جبار</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>الكرمة مركز الناحية</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (شمال البصرة)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:05:06.202</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5752607057</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>@ayutahoranx</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ايه محمود علي</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ابي الخصيب البهادريه</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>شركة الحفر العراقية</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:07:47.790</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>314635016</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>لا يوجد</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>حسين نعمان عبدالامير</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>الزبير</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>شركة ابن ماجد</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:08:28.624</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8596818143</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>@E_MU707</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>مقتدى ثائر زكي</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>منطقه النجيبيه</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>المديرية العامة لنقل الطاقة</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:08:45.108</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1338369872</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>@hr_4hh</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>حيدر اثير عبد الزهره</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>كرمه علي</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:08:48.883</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1479780975</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>@qqxqs</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>عبدالمحسن ناصر سواد</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>الهارثة/ كرمه علي</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (شمال البصرة)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:08:58.192</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1358399486</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>لا يوجد</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>زينب بشير عودة</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>جمعيات حي الخليج</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>المديرية العامة لنقل الطاقة</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:01.299</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6110884222</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>@uxw_10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>محمد نبراس كاظم</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ابي الخصيب /باب سليمان</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>الشركة العامة للبتروكيمياويات</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:04.449</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2114356745</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>@HEROX4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>محمد عبدالله عبدالقادر</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>حي المدراء</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>شركة ابن ماجد</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:08.478</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6414692425</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>@Ssssso8</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>محمود عقيل فهد</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ابي الخصيب</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (شمال البصرة)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:10.033</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6920645606</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>@imruqaia</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>رقيه ماجد حامد</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>المعقل</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>معهد التدريب النفطي</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:12.413</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2069592585</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>@mir8_15</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>مريم حيدر زبيد</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>الحيانية</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (البصرة)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:17.104</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5047925315</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>@mu7sabah</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>مصطفى صباح ذياب</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>مجمع الامل السكني</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (البصرة)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:17.660</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1432349602</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>@z7_lin</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>مصطفى هيثم كامل</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>الزبير</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>شركة ابن ماجد</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:17.661</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>272377394</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>@Alhassany16</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>علي مجتبى حسن</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>دور الصحة</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:18.787</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1168847165</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>@abs_m7</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>عباس فوزي عبدالله</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>البصرة القديمة</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>الشركة العامة لموانئ العراق</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:20.065</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>5393635699</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>@I6iyiv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>حسن صادق</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ابي الخصيب</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>شركة ابن ماجد</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:20.384</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>223170474</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>@Ahmed114477</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>احمد مصطفى جواد</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ابو الخصيب</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>الشركة العامة للبتروكيمياويات</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:26.368</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>806611565</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>@k_rba</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>كرار مهند نزار</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>شط العرب-الجزيره-الفحياء</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>الشركة العامة لموانئ العراق</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:28.521</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1359677440</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>@I0j_1i</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>عباس رائد عبد الحي</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>الفاو</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (البصرة)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:29.893</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1238181756</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>@saba0ll</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>سبأ عبدالرحمن خلف</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>الفنجانيه/المعقل</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>الشركة العامة لموانئ العراق</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:34.207</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>993887080</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>@vv7xo</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>محمد قصي عبدالباري</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>الجزيرة</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>مديرية بريد واتصالات</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:34.481</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1187987059</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>@MO7AMMED_KAZEM</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>محمد كاظم سالم</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ابي الخصيب</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>مديرية بريد واتصالات</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:35.285</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>204367555</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>@H910n</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>حسنين ناهي حنون</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>البصرة المعقل</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:35.553</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>5115244342</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>@eman2_m</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ايمان اياد كاظم</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>عنوان المعقل</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:37.346</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>915297090</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>@M_4N_S</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>مقتدى نعيم سليم</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>قضاء الدير</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (شمال البصرة)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:39.259</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>6817615480</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>لا يوجد</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>رسل حيدر علي</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>المعقل</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>الشركة العامة لموانئ العراق</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:41.260</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>5778714924</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>@kkajka</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>آمنة عبد الكريم قاسم</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>أبو الخصيب</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>المديرية العامة لنقل الطاقة</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:48.798</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1014305640</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>@Maryam_Sultan0</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>مريم عبد الرحمن سلطان</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>الزبير</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (شمال البصرة)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:52.157</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>653240537</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>@ir_skf</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>رضا صالح كاظم</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>القبلة</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:52.713</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>6385719057</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>@A0lld</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>احمد مكي حمزة</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>الجزيرة</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>مديرية بريد واتصالات</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:09:59.603</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1225613035</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>@nr_iq9</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ناصر زياد عبدالحافظ</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ابي الخصيب</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (البصرة)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:10:01.032</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>5691011196</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>@F3M1T</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>فاطمة مخلص ناصر</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>دور اسكان الطاقة</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:10:01.735</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1352365480</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>لا يوجد</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>حسن عبد الحافظ</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>البراضعية</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>مديرية بريد واتصالات</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:10:03.403</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1343201114</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>@VPN746</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>عباس عبد الحسين فيصل</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ابي الخصيب /حمدان</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (البصرة)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:10:05.276</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1078663467</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>@u60_s</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>محمد حسين علي جواد</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>شط العرب/الكباسي</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>مديرية بريد واتصالات</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:10:09.271</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1453270766</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>@Saife4u</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>سيف الدين اياد عبدالامير عزيز</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>التنومة الاكوات الثالثة</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (البصرة)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:10:16.327</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>804199962</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>@Sakina9l</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>سكينة أحمد عبد الحسين</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>البراضعية</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>مديرية بريد واتصالات</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:10:24.991</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1161073513</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>لا يوجد</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>علي فلاح حسن</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>حي المهندسين</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>شركة ابن ماجد</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:10:27.805</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>5083534620</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>@yccy5</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>حسين علي فالح</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>الموفقية</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>مديرية بريد واتصالات</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:10:30.107</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>6594964657</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>@zhzh_04</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>زهراء خالد محمد آمين</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>المعقل</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>المديرية العامة لنقل الطاقة</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:10:41.266</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>467690436</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>@Alyaahussein4</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>علياء حسين شهاب</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ياسين خريبط</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:10:46.400</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>429353971</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>@Massra_O</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>مسرة اسامة عبد الرزاق</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>دور الضباط</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:11:01.834</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1631077712</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>@MHTroo</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>محمد رحيم عبود</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>الطوبة والنخيلة</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>مديرية بريد واتصالات</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:11:26.936</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>6760480719</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>@ma_narr2004</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>منار مصطفى ابراهيم</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>خور الزبير</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>الشركة العامة للحديد والصلب</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:11:28.779</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1431355707</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>@tf_sh7</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>فاطمة شاكر سعيد</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>التنومة</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>مديرية بريد واتصالات</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:11:41.184</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>911849187</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>@ykz_9</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>عبدالرحمن عبدالكريم رمضان</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>مناوي لجم</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (البصرة)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:11:53.516</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>801593449</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>@mj42t</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>مجتبى منتظر جعفر</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>المشراق الجديد</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (البصرة)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:11:59.381</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1119896672</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>@jaa_r8</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>جعفر محمد جبار</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>المعقل</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (شمال البصرة)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:12:00.295</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2044646848</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>@jjkhhx</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>زينب منتظر عبدالرضا</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>الفاو</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (البصرة)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:12:04.487</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1815406110</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>@fano_21a</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>افنان محمد شهاب</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>الزبير _ محلة الكوت</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>شركة ابن ماجد</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:12:06.284</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>469991428</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>@ax7ka</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>عبدالله مشتاق حسن</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>التنومة</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:12:59.196</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>787979672</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>@x85o0</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>احمد علاء حسن</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>التنومة</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:13:07.227</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>6820223477</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>لا يوجد</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>زهراء صلاح جميل</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>الجبيله</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (البصرة)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:13:09.062</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>6453602117</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>@uytwer</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>نبأ عبدالله نجم</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>الاكوات</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (شمال البصرة)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:13:33.407</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1443891935</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>@Haider_AL_Batat</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>حيدر محمد حسن</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>كرمة علي ابي صخير</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (شمال البصرة)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:13:41.961</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1341616090</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>@Ij_or</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>مسلم عقيل طاهر</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>قرنه</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (البصرة)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:15:08.101</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1242756624</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>@a_s5tr</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>عطاالله منير منعم</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>حي الخضراء</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>المديرية العامة لنقل الطاقة</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:15:52.666</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>6390086533</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>@Batolll_313</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>بتول عيدان عبد</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ابي الخصيب</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>الشركة العامة لصناعة الاسمدة</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:17:04.683</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>1033235961</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>لا يوجد</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>علي يوسف حسن</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ابو الخصيب</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>مديرية بريد واتصالات</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:17:36.576</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>8575842452</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>@k_xgr</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>كرار كاظم هزاع</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>القرنة</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (شمال البصرة)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:17:59.764</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>1102872962</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>@t0ety1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>روان رائد مهدي</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>المطيحة</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>شركة ابن ماجد</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:18:17.250</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>5585032442</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>لا يوجد</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>حوراء باسم عبد الحسين</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ابي الخصيب</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:18:41.431</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>7162453100</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>@Mun_meme</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>مؤمن عبدالرسول بجاي شري</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>المعقل-الابلة</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:18:52.221</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>5951334465</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>@manarrafid18</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>منار رافد محمد</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>المعقل</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:19:00.079</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>7667790555</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>@ebtehal_ss</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ابتهال ناجح بدر</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>الطويسه</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>المديرية العامة لنقل الطاقة</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:21:01.218</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>1146077031</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>@Reeim22</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>مريم نجم عبد</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>السكن (الجمهورية)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:22:14.125</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>1030940597</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>لا يوجد</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>حيدر مازن سالم</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>حي المدراء</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>شركة ابن ماجد</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:29:24.227</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>5755758554</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>@Fa225l</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>فاطمة شاكر عبود</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>الفاو</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>مديرية بريد واتصالات</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:29:28.016</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>1550043915</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>@hh_t10</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>الاسم: حيدر علاء عبد الامير</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>عنوان السكن: قضاء القرنة</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (شمال البصرة)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:31:11.040</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>1001528724</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>@aawt12</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>محمد عبود علي</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>قضاء الفاو</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:34:27.717</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>1071283028</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>@MohN_2003</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>محمد ناظم مال الله</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ناحية ام قصر</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (شمال البصرة)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:36:20.962</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2027289076</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>@Zozoyko</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>زينب مثنى عودة</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>الهارثة</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:37:30.019</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>5608076430</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>لا يوجد</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ماجده معاذ</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>المعقل</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:38:31.960</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2126669053</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>@RR_2R</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>مجتبى كريم بنيان</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>الزبير</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>شركة ابن ماجد</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:41:59.096</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>743446905</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>@ad_r3</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>احمد رعد عبدالرزاق</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>شط العرب التنومه الاكوات الاولى</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (شمال البصرة)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:48:37.393</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>1480531026</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>@abbasrrt</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>عباس راضي حسين</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>كرمة علي اللطيف</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:53:03.167</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>803606284</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>@Mohamed_mohm</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>محمد مردان عبد الكريم</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>حي الخضراء</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>شركة توزيع المنتجات النفطية</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:59:14.078</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>6454602535</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>لا يوجد</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>فاطمة ليث سلمان</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ابي الخصيب</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>شركة توزيع المنتجات النفطية</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-05-13 22:00:57.679</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>835744152</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>@m_d5mm</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ضحى محمود عبدالهادي</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ابي الخصيب</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>شركة توزيع المنتجات النفطية</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-05-13 22:04:53.671</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>968544105</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>@itsmjtba</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>مجتبى قيصر سمير</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>كرمة علي / البدران</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-05-13 22:08:41.348</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>422085695</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>@Haider_Ismail5</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>الاسم : حيدر إسماعيل خليل</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>العنوان : البصرة _قضاء الفاو</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>الشركة العامة لصناعة الاسمدة</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-05-13 22:14:50.583</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>1436284670</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>@raw_614</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>روان سمير حسين</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>الزبير</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>شركة ابن ماجد</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-05-13 22:15:33.924</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>6619103374</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>@mraiaam</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>مريم احمد بريسم</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>البرجسية</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>شركة الحفر العراقية</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-05-13 22:21:30.435</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>5327999169</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>@tm_m9</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>محمد حازم تاج</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>حي الزهور</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>شركة ابن ماجد</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-05-13 22:29:48.830</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>6928182060</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>@MOJTABA_SABAH2</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>مجتبى صباح عطيه</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>شط العرب - التنومه</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-05-13 22:38:44.380</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>6310707662</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>@noofriyadh2</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>نوف رياض يوسف</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>الجزائر</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>الشركة العامة للحديد والصلب</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2026-05-13 22:49:25.048</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>1428763151</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>@t52za</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>زهراء حيدر فالح</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ابي الخصيب</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-05-13 22:57:36.578</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1437786932</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>@Yahthatme</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>محمد امجد عبدالحميد</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ابي الخصيب - باب سليمان</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>مركز التدريب المهني</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-05-13 23:50:49.079</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>925433865</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>@Mkgskp</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>مهدي محمد رسن</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>كرمه علي الناحيه</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-05-13 23:57:41.025</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>566781672</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>@ha3_z</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>الاسم : حسن علي صحن</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>العنوان : حي الحسين /شارع السيد</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2026-05-14 00:15:15.531</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>6274351316</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>@ezxcz</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>علي حيدر جاسم</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>البصرة دور الضباط</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-05-14 00:37:33.084</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>5617236389</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>لا يوجد</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>مهدي مرتضى سبتي</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>الحيانية (حي الحسين)</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>شركة توزيع المنتجات النفطية</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026-05-14 07:51:12.822</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>6964929872</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>@Eng_ElecF</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>فاطمة بهاء عبد الرضا</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>الگرمة</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>شركة مصافي الجنوب</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:51:32.530</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1400567580</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>@N_za95</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>نبأ محمد يوسف</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>أبو الخصيب</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>مديرية بريد واتصالات</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:59:52.781</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>616125546</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>@k7_al8</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>اباالحسن نجم عبدالسيد</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>قضاء الفاو</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2026-05-14 14:13:12.666</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>8191192378</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>@c_os50</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>كرار حيدر كاظم</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>قضاء الفاو</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2026-05-14 14:14:15.577</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1436378245</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>@Zallak55</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>زهراء شوقي مهاوي</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>حي الرضا</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026-05-14 14:57:07.672</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>8142451913</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>@Fah10_10</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>فاطمة ثائر جبار</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ابو الخصيب</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>شركة مصافي الجنوب</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026-05-14 17:40:10.313</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1388593996</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>@Hus_Munaf</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>حسين مناف</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>البصرة قضاء الفاو</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026-05-14 17:52:43.228</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>6819820522</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>لا يوجد</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>الفواطم فراس طاهر</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>الاصمعي حي الاستاذة</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2026-05-14 17:56:46.225</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>5023969424</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>@t0_iil</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>طيبة كاظم زيارة</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>دور الضباط</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (البصرة)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2026-05-14 20:25:36.465</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>6446944413</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>@sss_n5</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>سجاد حسن شنشول</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>الامن الداخلي</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>شركة مصافي الجنوب</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026-05-15 07:40:37.996</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1829633331</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>@anef2</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>محمد رياض طالب</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>كرمة علي</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2026-05-15 16:37:48.834</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>7386689918</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>لا يوجد</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>الإسم/زهراء وليد صبر</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>السكن/ المعقل</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2026-05-15 20:16:58.734</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>5310996739</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>@SZ6_1</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>سيف نبراس مهدي</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>نظران</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>شركة مصافي الجنوب</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2026-05-15 20:27:28.436</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>5296890397</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>@mogtaba_albaag</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>مجتبى هشام جمعة</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>المشراق الجديد</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>الشركة العامة للحديد والصلب</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2026-05-15 20:57:57.706</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>8532139503</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>لا يوجد</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>زينب وليد عبد الحميد خضير</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>الزبير</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>شركة الحفر العراقية</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:32:16.787</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>1361967872</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>@AT23ye</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>حسن عبدالصاحب كاطع</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>كرمة علي</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2026-05-16 02:59:47.083</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>212565046</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>@Ali_Hassan_02</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>علي حسن كريم</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>الزبير</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>شركة ابن ماجد</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2026-05-16 09:10:43.604</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>518587801</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>@ch5h5</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>علي احمد خيرالله</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>عنوان السكن : الاندلس</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2026-05-16 12:02:35.422</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
